--- a/MODS_List.xlsx
+++ b/MODS_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft Mods\MODS LIST SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8C3E2E-D95C-4BC0-8DF1-4D4B270326DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF989FD-3198-4582-89ED-843677F0C596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="6" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="8" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
   </bookViews>
   <sheets>
     <sheet name="1.21.1" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,31 @@
     <sheet name="1.21.8" sheetId="5" r:id="rId5"/>
     <sheet name="1.21.10" sheetId="6" r:id="rId6"/>
     <sheet name="1.21.11" sheetId="7" r:id="rId7"/>
+    <sheet name="26.1.1" sheetId="8" r:id="rId8"/>
+    <sheet name="26.1.2" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="62">
   <si>
     <t>No</t>
   </si>
@@ -205,6 +218,18 @@
   </si>
   <si>
     <t>MC JAVA 1.21.11</t>
+  </si>
+  <si>
+    <t>26.1.1</t>
+  </si>
+  <si>
+    <t>MC JAVA 26.1.1</t>
+  </si>
+  <si>
+    <t>26.1.2</t>
+  </si>
+  <si>
+    <t>MC JAVA 26.1.2</t>
   </si>
 </sst>
 </file>
@@ -320,7 +345,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -538,9 +619,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -578,7 +659,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -684,7 +765,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -826,7 +907,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1237,18 +1318,18 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="27" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="35" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 E7:E14 E16:E24">
-    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1711,18 +1792,18 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="23" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="31" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="30" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="28" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2105,6 +2186,959 @@
       <c r="E23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Not Available</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F27"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
+    <cfRule type="notContainsBlanks" dxfId="27" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
+    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475DB82D-BD27-4169-970A-0C1118323223}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F27"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
+    <cfRule type="notContainsBlanks" dxfId="23" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BD3BE8-05D7-4456-A946-367EC5D24219}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
       </c>
       <c r="F23" s="10"/>
     </row>
@@ -2201,959 +3235,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475DB82D-BD27-4169-970A-0C1118323223}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>5</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>8</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>10</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>12</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F27"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BD3BE8-05D7-4456-A946-367EC5D24219}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>5</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>8</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>10</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>12</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F27"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="11" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3665,18 +3746,18 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3985,11 +4066,11 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F19" s="10"/>
     </row>
@@ -4140,11 +4221,1061 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="11" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9AE51B-23A7-4AA8-8C62-6DF59BEA789A}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
       <c r="E28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Not Available</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="7" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CF120B-E68B-46D5-A99B-5EC64B08171D}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
       </c>
       <c r="F28" s="10"/>
     </row>

--- a/MODS_List.xlsx
+++ b/MODS_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft Mods\MODS LIST SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF989FD-3198-4582-89ED-843677F0C596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C278FCE6-AB48-4545-B32E-A40527F08546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="8" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
   </bookViews>
@@ -5338,5 +5338,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MODS_List.xlsx
+++ b/MODS_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft Mods\MODS LIST SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C278FCE6-AB48-4545-B32E-A40527F08546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829E97A1-0823-4780-ADF1-11C7E47FD033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="8" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="9" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
   </bookViews>
   <sheets>
     <sheet name="1.21.1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="1.21.11" sheetId="7" r:id="rId7"/>
     <sheet name="26.1.1" sheetId="8" r:id="rId8"/>
     <sheet name="26.1.2" sheetId="9" r:id="rId9"/>
+    <sheet name="26.2" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="63">
   <si>
     <t>No</t>
   </si>
@@ -230,6 +231,9 @@
   </si>
   <si>
     <t>MC JAVA 26.1.2</t>
+  </si>
+  <si>
+    <t>26.2</t>
   </si>
 </sst>
 </file>
@@ -345,7 +349,35 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="40">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1318,23 +1350,548 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="35" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="39" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 E7:E14 E16:E24">
-    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="38" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141C2AF4-AF47-46DD-A3C3-964BA4D4656A}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1789,6 +2346,480 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="F4:F27"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
+    <cfRule type="notContainsBlanks" dxfId="35" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E520F1-94DC-4808-A079-08759849691F}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F27"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 C7:C14 C16:C24">
@@ -1812,21 +2843,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E520F1-94DC-4808-A079-08759849691F}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475DB82D-BD27-4169-970A-0C1118323223}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1873,7 +2904,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2062,11 +3093,11 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F16" s="10"/>
     </row>
@@ -2079,11 +3110,11 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F17" s="10"/>
     </row>
@@ -2128,13 +3159,15 @@
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
+        <v>ALT</v>
       </c>
       <c r="F20" s="10"/>
     </row>
@@ -2164,11 +3197,11 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F22" s="10"/>
     </row>
@@ -2179,13 +3212,15 @@
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>ALT</v>
       </c>
       <c r="F23" s="10"/>
     </row>
@@ -2215,11 +3250,11 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F25" s="10"/>
     </row>
@@ -2282,12 +3317,11 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475DB82D-BD27-4169-970A-0C1118323223}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BD3BE8-05D7-4456-A946-367EC5D24219}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2300,7 +3334,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2347,7 +3381,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2600,17 +3634,15 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="C20" s="2"/>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ALT</v>
+        <v>OK</v>
       </c>
       <c r="F20" s="10"/>
     </row>
@@ -2656,7 +3688,7 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
@@ -2693,11 +3725,11 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
+        <v>Not Available</v>
       </c>
       <c r="F25" s="10"/>
     </row>
@@ -2763,481 +3795,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BD3BE8-05D7-4456-A946-367EC5D24219}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>5</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>8</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>10</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>12</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F27"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="19" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F7259F-1FDA-4086-A7B3-32866E9EF768}">
   <dimension ref="A1:F30"/>
@@ -3746,18 +4303,18 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="19" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4226,6 +4783,532 @@
       <c r="E28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9AE51B-23A7-4AA8-8C62-6DF59BEA789A}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
       </c>
       <c r="F28" s="10"/>
     </row>
@@ -4291,8 +5374,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9AE51B-23A7-4AA8-8C62-6DF59BEA789A}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CF120B-E68B-46D5-A99B-5EC64B08171D}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4305,7 +5388,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4352,7 +5435,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4461,11 +5544,11 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -4546,11 +5629,11 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F16" s="10"/>
     </row>
@@ -4575,11 +5658,11 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F18" s="10"/>
     </row>
@@ -4592,11 +5675,11 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F19" s="10"/>
     </row>
@@ -4609,11 +5692,11 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F20" s="10"/>
     </row>
@@ -4677,11 +5760,11 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F24" s="10"/>
     </row>
@@ -4690,17 +5773,15 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ALT</v>
+        <v>OK</v>
       </c>
       <c r="F25" s="10"/>
     </row>
@@ -4730,11 +5811,11 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F27" s="10"/>
     </row>
@@ -4747,11 +5828,11 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F28" s="10"/>
     </row>
@@ -4814,530 +5895,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CF120B-E68B-46D5-A99B-5EC64B08171D}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>9</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>10</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>12</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F30" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F30"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B17:E17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MODS_List.xlsx
+++ b/MODS_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft Mods\MODS LIST SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829E97A1-0823-4780-ADF1-11C7E47FD033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B26172-B7F4-4587-9122-E0B6E4FAD2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="9" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="64">
   <si>
     <t>No</t>
   </si>
@@ -185,24 +185,6 @@
     <t>Reese's Sodium Option</t>
   </si>
   <si>
-    <t>MC JAVA 1.21.1</t>
-  </si>
-  <si>
-    <t>MC JAVA 1.21.4</t>
-  </si>
-  <si>
-    <t>MC JAVA 1.21.5</t>
-  </si>
-  <si>
-    <t>MC JAVA 1.21.6</t>
-  </si>
-  <si>
-    <t>MC JAVA 1.21.8</t>
-  </si>
-  <si>
-    <t>MC JAVA 1.21.10</t>
-  </si>
-  <si>
     <t>Chunky</t>
   </si>
   <si>
@@ -218,22 +200,43 @@
     <t>1.21.11</t>
   </si>
   <si>
-    <t>MC JAVA 1.21.11</t>
-  </si>
-  <si>
     <t>26.1.1</t>
   </si>
   <si>
-    <t>MC JAVA 26.1.1</t>
-  </si>
-  <si>
     <t>26.1.2</t>
   </si>
   <si>
-    <t>MC JAVA 26.1.2</t>
-  </si>
-  <si>
     <t>26.2</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.1</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.4</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.5</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.6</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.8</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.10</t>
+  </si>
+  <si>
+    <t>Fabric 1.21.11</t>
+  </si>
+  <si>
+    <t>Fabric 26.1.1</t>
+  </si>
+  <si>
+    <t>Fabric 26.1.2</t>
+  </si>
+  <si>
+    <t>Fabric 26.2</t>
   </si>
 </sst>
 </file>
@@ -959,7 +962,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1384,7 +1387,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1431,7 +1434,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1621,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
@@ -1718,7 +1721,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="1">
@@ -1786,7 +1789,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="1">
@@ -1854,7 +1857,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">
@@ -1909,7 +1912,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2383,7 +2386,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2857,7 +2860,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3334,7 +3337,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3809,7 +3812,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4046,7 +4049,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
@@ -4143,7 +4146,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="1">
@@ -4213,7 +4216,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="1">
@@ -4281,7 +4284,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">
@@ -4336,7 +4339,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4383,7 +4386,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4573,7 +4576,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
@@ -4670,7 +4673,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="1">
@@ -4740,7 +4743,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="1">
@@ -4808,7 +4811,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">
@@ -4862,7 +4865,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4909,7 +4912,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5099,7 +5102,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
@@ -5196,7 +5199,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="1">
@@ -5266,7 +5269,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="1">
@@ -5334,7 +5337,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">
@@ -5388,7 +5391,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5435,7 +5438,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5625,7 +5628,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1">
@@ -5722,7 +5725,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="1">
@@ -5790,7 +5793,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="1">
@@ -5858,7 +5861,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">

--- a/MODS_List.xlsx
+++ b/MODS_List.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft Mods\MODS LIST SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B26172-B7F4-4587-9122-E0B6E4FAD2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4565885-B11A-4F37-9D02-4EA8BF61F2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="9" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E74ECB2E-996A-4875-884C-8D1C5172DCE7}"/>
   </bookViews>
   <sheets>
-    <sheet name="1.21.1" sheetId="1" r:id="rId1"/>
-    <sheet name="1.21.4" sheetId="2" r:id="rId2"/>
-    <sheet name="1.21.5" sheetId="3" r:id="rId3"/>
-    <sheet name="1.21.6" sheetId="4" r:id="rId4"/>
-    <sheet name="1.21.8" sheetId="5" r:id="rId5"/>
-    <sheet name="1.21.10" sheetId="6" r:id="rId6"/>
-    <sheet name="1.21.11" sheetId="7" r:id="rId7"/>
-    <sheet name="26.1.1" sheetId="8" r:id="rId8"/>
-    <sheet name="26.1.2" sheetId="9" r:id="rId9"/>
-    <sheet name="26.2" sheetId="10" r:id="rId10"/>
+    <sheet name="26.2" sheetId="10" r:id="rId1"/>
+    <sheet name="26.1.2" sheetId="9" r:id="rId2"/>
+    <sheet name="26.1.1" sheetId="8" r:id="rId3"/>
+    <sheet name="1.21.11" sheetId="7" r:id="rId4"/>
+    <sheet name="1.21.10" sheetId="6" r:id="rId5"/>
+    <sheet name="1.21.8" sheetId="5" r:id="rId6"/>
+    <sheet name="1.21.6" sheetId="4" r:id="rId7"/>
+    <sheet name="1.21.5" sheetId="3" r:id="rId8"/>
+    <sheet name="1.21.4" sheetId="2" r:id="rId9"/>
+    <sheet name="1.21.1" sheetId="1" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -949,6 +949,531 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141C2AF4-AF47-46DD-A3C3-964BA4D4656A}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B706093F-AB4D-4559-B913-F63F8F629CBD}">
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1373,8 +1898,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141C2AF4-AF47-46DD-A3C3-964BA4D4656A}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CF120B-E68B-46D5-A99B-5EC64B08171D}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1387,7 +1912,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1434,7 +1959,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1861,11 +2386,11 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Not Available</v>
+        <v>OK</v>
       </c>
       <c r="F30" s="10"/>
     </row>
@@ -1878,18 +2403,18 @@
     <mergeCell ref="B17:E17"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1898,21 +2423,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3601DE9-5D61-4A26-B9A8-CDD1F1D318A6}">
-  <dimension ref="A1:F27"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9AE51B-23A7-4AA8-8C62-6DF59BEA789A}">
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1959,7 +2484,1586 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>32</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="11" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17872053-FD3C-425B-A7A3-BB452EA8DB93}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F30"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F7259F-1FDA-4086-A7B3-32866E9EF768}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" ref="E9:E29" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Available</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" ref="E30" si="1">_xlfn.IFS(D30=0,"Not Available",D30=1,"OK",D30=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F30" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F4:F30"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
+    <cfRule type="notContainsBlanks" dxfId="19" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BD3BE8-05D7-4456-A946-367EC5D24219}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2212,7 +4316,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="1">
@@ -2265,13 +4369,15 @@
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
+        <v>ALT</v>
       </c>
       <c r="F23" s="10"/>
     </row>
@@ -2301,11 +4407,11 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
+        <v>Not Available</v>
       </c>
       <c r="F25" s="10"/>
     </row>
@@ -2346,33 +4452,509 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F27"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F4:F27"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="35" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="23" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475DB82D-BD27-4169-970A-0C1118323223}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
+        <v>OK</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ALT</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:F27"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
+    <cfRule type="notContainsBlanks" dxfId="27" priority="1">
+      <formula>LEN(TRIM(C5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
+    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="ALT">
+      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E520F1-94DC-4808-A079-08759849691F}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2846,21 +5428,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475DB82D-BD27-4169-970A-0C1118323223}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3601DE9-5D61-4A26-B9A8-CDD1F1D318A6}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2907,7 +5489,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3162,15 +5744,13 @@
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="C20" s="2"/>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ALT</v>
+        <v>OK</v>
       </c>
       <c r="F20" s="10"/>
     </row>
@@ -3215,15 +5795,13 @@
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ALT</v>
+        <v>OK</v>
       </c>
       <c r="F23" s="10"/>
     </row>
@@ -3298,2606 +5876,28 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F27"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F4:F27"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="27" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="35" priority="1">
       <formula>LEN(TRIM(C5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="ALT">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="ALT">
       <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Not Available">
+    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Not Available">
       <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BD3BE8-05D7-4456-A946-367EC5D24219}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>_xlfn.IFS(D7=0,"Not Available",D7=1,"OK",D7=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" ref="E8:E27" si="0">_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>5</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>8</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>10</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>12</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F27"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5 C7:C14 C16:C24">
-    <cfRule type="notContainsBlanks" dxfId="23" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14 E16:E27">
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F7259F-1FDA-4086-A7B3-32866E9EF768}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" ref="E9:E29" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>9</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>10</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>12</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f t="shared" ref="E30" si="1">_xlfn.IFS(D30=0,"Not Available",D30=1,"OK",D30=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F30" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F4:F30"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="19" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17872053-FD3C-425B-A7A3-BB452EA8DB93}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>9</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>10</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>12</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F30" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F30"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B17:E17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9AE51B-23A7-4AA8-8C62-6DF59BEA789A}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>9</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ALT</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>10</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>12</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F30" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F30"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B17:E17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="11" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CF120B-E68B-46D5-A99B-5EC64B08171D}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.IFS(D5=0,"Not Available",D5=1,"OK",D5=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>_xlfn.IFS(D6=0,"Not Available",D6=1,"OK",D6=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>_xlfn.IFS(D8=0,"Not Available",D8=1,"OK",D8=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" ref="E9:E30" si="0">_xlfn.IFS(D9=0,"Not Available",D9=1,"OK",D9=2,"ALT")</f>
-        <v>OK</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>9</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Available</v>
-      </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>10</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>12</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="F30" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F30"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B17:E17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C6 C8:C16 C18:C30">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="1">
-      <formula>LEN(TRIM(C5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6 E8:E16 E18:E30">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="ALT">
-      <formula>NOT(ISERROR(SEARCH("ALT",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Not Available">
-      <formula>NOT(ISERROR(SEARCH("Not Available",E5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>